--- a/AAII_Financials/Quarterly/ORIC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORIC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="92">
   <si>
     <t>ORIC</t>
   </si>
@@ -656,150 +656,154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -842,8 +846,8 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -899,8 +903,11 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1000,8 +1007,11 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1101,8 +1111,11 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1138,109 +1151,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E12" s="3">
         <v>31400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>28800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>31200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>28900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>18800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>19700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>16800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>16700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>15500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>11700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>5600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>5000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>5200</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1340,8 +1357,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1384,56 +1404,56 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
         <v>11900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>13000</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>3</v>
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1441,8 +1461,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1486,7 +1509,7 @@
         <v>300</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1542,8 +1565,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1576,210 +1602,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E17" s="3">
         <v>39600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>39100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>32700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>38300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>22100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>16600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>28300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>25600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>11100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6300</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-45300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-39600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-34600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-36700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-39100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-32700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-39600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-38300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-36000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-29000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-31400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-28700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-25000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-22100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-25700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-20700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-23300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-22800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-18500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-21100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-16600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-28300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-25600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-8800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-6400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1815,8 +1848,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1859,21 +1893,21 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1887,138 +1921,144 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
       </c>
       <c r="AB20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-45000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-39300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-34200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-36400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-38800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-32400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-39300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-38000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-35700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-28700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-31200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-28400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-24700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-20600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-24600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-20000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-22900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-22500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-18200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-20800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-25300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2061,8 +2101,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2118,100 +2158,103 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-35800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-30500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-32600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-36400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-36300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-34600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-32000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-22900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-24800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-20300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-23200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-22800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-18400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-21000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-28300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-25500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-8400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-6000</v>
       </c>
       <c r="AF23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
+      <c r="AG23" s="3">
+        <v>-6000</v>
       </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
@@ -2219,8 +2262,11 @@
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2263,8 +2309,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2320,8 +2366,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2421,100 +2470,103 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-30500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-32600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-36400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-30000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-36300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-32000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-22900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-24800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-20300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-23200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-22800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-18400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-21000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-28300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-25500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-8400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>-6000</v>
       </c>
       <c r="AF26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
+      <c r="AG26" s="3">
+        <v>-6000</v>
       </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
@@ -2522,100 +2574,103 @@
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-30500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-32600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-36400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-30000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-36300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-34600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-32000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-22900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-24800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-20300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-23200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-22800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-18400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-21000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-28300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-25500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-8400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>-6000</v>
       </c>
       <c r="AF27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
+      <c r="AG27" s="3">
+        <v>-6000</v>
       </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
@@ -2623,8 +2678,11 @@
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2724,8 +2782,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2825,8 +2886,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2926,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3027,8 +3094,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3071,21 +3141,21 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -3099,129 +3169,132 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
       </c>
       <c r="AB32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-35800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-30500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-32600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-36400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-30000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-36300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-34600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-32000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-22900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-24800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-23200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-22800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-18400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-21000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-28300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-25500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-8400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>-6000</v>
       </c>
       <c r="AF33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
+      <c r="AG33" s="3">
+        <v>-6000</v>
       </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
@@ -3229,8 +3302,11 @@
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3330,100 +3406,103 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-35800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-30500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-32600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-36400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-30000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-36300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-34600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-32000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-22900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-24800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-23200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-22800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-18400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-21000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-28300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-25500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-8400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>-6000</v>
       </c>
       <c r="AF35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
+      <c r="AG35" s="3">
+        <v>-6000</v>
       </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
@@ -3431,114 +3510,120 @@
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3574,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3611,89 +3697,90 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E41" s="3">
         <v>56400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>45700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>75900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>59400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>44200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>49800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>56400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>103700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>59000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>66800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>29100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>49100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>112600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>226000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>241100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>170100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>104200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>78400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>62000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>196600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>79400</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3712,83 +3799,86 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>227300</v>
+      </c>
+      <c r="E42" s="3">
         <v>225500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>235800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>237500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>206600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>154400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>196600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>228100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>236600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>260400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>184800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>201100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>160500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>130600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>139400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>164600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>178000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>122000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>11000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>48400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>91000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>173900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>215200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>124600</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3804,8 +3894,8 @@
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG42" s="3">
-        <v>0</v>
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH42" s="3">
         <v>0</v>
@@ -3813,8 +3903,11 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3857,8 +3950,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -3914,8 +4007,11 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3958,8 +4054,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4015,8 +4111,11 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4059,45 +4158,45 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>4200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>800</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4116,89 +4215,92 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>273700</v>
+      </c>
+      <c r="E46" s="3">
         <v>290200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>288500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>295600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>291100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>211400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>262300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>279400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>294600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>324100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>212600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>232200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>268400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>193200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>210500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>198700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>233500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>239100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>240500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>292800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>265000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>280100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>296700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>189100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>199200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>80200</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,71 +4319,74 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E47" s="3">
         <v>137800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>110800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>125900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>45200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>20000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>10000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>22100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>14700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>26900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>28900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>19300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>22000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>24300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>10800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>21600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>43400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4297,8 +4402,8 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -4318,89 +4423,92 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3300</v>
-      </c>
-      <c r="R48" s="3">
-        <v>3000</v>
       </c>
       <c r="S48" s="3">
         <v>3000</v>
       </c>
       <c r="T48" s="3">
+        <v>3000</v>
+      </c>
+      <c r="U48" s="3">
         <v>2500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2400</v>
-      </c>
-      <c r="V48" s="3">
-        <v>1800</v>
       </c>
       <c r="W48" s="3">
         <v>1800</v>
       </c>
       <c r="X48" s="3">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="Y48" s="3">
         <v>2000</v>
       </c>
       <c r="Z48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA48" s="3">
         <v>1900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2100</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4419,8 +4527,11 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4520,8 +4631,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4621,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4722,89 +4839,92 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E52" s="3">
         <v>6600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2700</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4943,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4924,89 +5047,92 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>404700</v>
+      </c>
+      <c r="E54" s="3">
         <v>436800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>408900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>431200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>346900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>242900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>274100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>302100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>328900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>350800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>252000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>274300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>291800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>226600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>247200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>238000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>259700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>275100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>298600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>314200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>268200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>284000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>299000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>191700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>201500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>85100</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5025,8 +5151,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5062,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5099,89 +5229,90 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>800</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5200,8 +5331,11 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5218,16 +5352,16 @@
         <v>3300</v>
       </c>
       <c r="H58" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="I58" s="3">
         <v>3200</v>
       </c>
       <c r="J58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K58" s="3">
         <v>3100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2800</v>
       </c>
       <c r="L58" s="3">
         <v>2800</v>
@@ -5236,7 +5370,7 @@
         <v>2800</v>
       </c>
       <c r="N58" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="O58" s="3">
         <v>2700</v>
@@ -5245,7 +5379,7 @@
         <v>2700</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5301,8 +5435,11 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5345,45 +5482,45 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>14100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4000</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5402,89 +5539,92 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E60" s="3">
         <v>17800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>15200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4800</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5503,53 +5643,56 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E61" s="3">
         <v>3400</v>
-      </c>
-      <c r="E61" s="3">
-        <v>4100</v>
       </c>
       <c r="F61" s="3">
         <v>4100</v>
       </c>
       <c r="G61" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H61" s="3">
         <v>4800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5604,8 +5747,11 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5648,45 +5794,45 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
         <v>9400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>10200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>10500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>10700</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
       <c r="X62" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="3">
         <v>200</v>
       </c>
       <c r="Z62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA62" s="3">
         <v>400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>600</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5705,8 +5851,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5806,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5907,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6008,89 +6163,92 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E66" s="3">
         <v>21200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>31000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>24800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>22800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>22000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>25700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5400</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6109,8 +6267,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6146,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6247,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6348,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6426,11 +6594,11 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>178100</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
@@ -6449,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6550,89 +6721,92 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-769500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-728000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-692200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-661700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-629200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-592800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-562800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-526500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-491900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-459900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-434900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-406600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-381100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-358200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-335500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-315100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-289800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-269100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-245200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-222300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-203900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-182900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-166400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-138200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-112600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-101600</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6651,8 +6825,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6752,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6853,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6954,89 +7137,92 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>381300</v>
+      </c>
+      <c r="E76" s="3">
         <v>415600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>384400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>406900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>324000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>219700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>243100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>274000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>302400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>328600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>224100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>247400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>268800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>202800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>222400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>214800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>236900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>253100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>273000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>291500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>258300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>276100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>289800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>184400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>195200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-98400</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7055,8 +7241,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7156,206 +7345,212 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-35800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-30500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-32600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-36400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-30000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-36300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-34600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-32000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-22900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-24800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-23200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-22800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-18400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-21000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-28300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-25500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-8400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>-6000</v>
       </c>
       <c r="AF81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
+      <c r="AG81" s="3">
+        <v>-6000</v>
       </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
@@ -7363,8 +7558,11 @@
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7400,8 +7598,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7433,7 +7632,7 @@
         <v>300</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
@@ -7442,10 +7641,10 @@
         <v>200</v>
       </c>
       <c r="P83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
@@ -7454,10 +7653,10 @@
         <v>200</v>
       </c>
       <c r="T83" s="3">
+        <v>200</v>
+      </c>
+      <c r="U83" s="3">
         <v>300</v>
-      </c>
-      <c r="U83" s="3">
-        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
@@ -7478,7 +7677,7 @@
         <v>200</v>
       </c>
       <c r="AB83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC83" s="3">
         <v>300</v>
@@ -7487,13 +7686,13 @@
         <v>300</v>
       </c>
       <c r="AE83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AF83" s="3">
         <v>200</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
+      <c r="AG83" s="3">
+        <v>200</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
@@ -7501,8 +7700,11 @@
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7602,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7703,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7804,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7905,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8006,100 +8220,103 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-22500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-25100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-32500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-25600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-19300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-22700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-16300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-12100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-16200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-14900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-17800</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-9600</v>
       </c>
       <c r="AA89" s="3">
         <v>-9600</v>
       </c>
       <c r="AB89" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-8300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-5400</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>-5500</v>
       </c>
       <c r="AF89" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
+      <c r="AG89" s="3">
+        <v>-5500</v>
       </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
@@ -8107,8 +8324,11 @@
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8144,109 +8364,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-400</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
       <c r="R91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S91" s="3">
         <v>-400</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-700</v>
       </c>
       <c r="T91" s="3">
         <v>-700</v>
       </c>
       <c r="U91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8346,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8447,109 +8674,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>17000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-110500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-76900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>22500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>42700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>23100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>18300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-61900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>21000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-57800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>12800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>28300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-46200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-90700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>35100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>82400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>40600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-91300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-124700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8585,8 +8818,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8629,8 +8863,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8686,8 +8920,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8787,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8888,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8989,109 +9232,115 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800</v>
+      </c>
+      <c r="E100" s="3">
         <v>61100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>109500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>134300</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>125000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>85200</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>24800</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>48600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-300</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>125500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>127000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>5700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>49900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>15300</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9134,8 +9383,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -9191,105 +9440,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E102" s="3">
         <v>10700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-26200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>26500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>33000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-77400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>44700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>37800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-20000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-63600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-113400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-15100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>71500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>65900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>25800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>16400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-134600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>117200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-9700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-7300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>44000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>9600</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
